--- a/GF_X-master/AAAGameData/Languages/ChineseSimplified.xlsx
+++ b/GF_X-master/AAAGameData/Languages/ChineseSimplified.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\UnityProjects\UGF\AAAGameData\Languages\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A27FB5F-DA67-4F4E-88AC-01C7EA57985C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Anonymous</author>
   </authors>
@@ -63,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>BRAKE</t>
   </si>
@@ -77,6 +84,12 @@
     <t>引擎</t>
   </si>
   <si>
+    <t>FailGame</t>
+  </si>
+  <si>
+    <t>你被老板发现，立刻被开除了，从此流落街头，点击重来逆转时间</t>
+  </si>
+  <si>
     <t>GET</t>
   </si>
   <si>
@@ -119,6 +132,12 @@
     <t>点击开始</t>
   </si>
   <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>干得漂亮！</t>
+  </si>
+  <si>
     <t>Nothing</t>
   </si>
   <si>
@@ -143,12 +162,6 @@
     <t>取消</t>
   </si>
   <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>喜欢这款游戏吗?\n请给个5星好评吧!</t>
-  </si>
-  <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
@@ -239,6 +252,12 @@
     <t>驾驶</t>
   </si>
   <si>
+    <t>SuccessGame</t>
+  </si>
+  <si>
+    <t>你成功俘获了老板女儿的芳心，立刻迎娶了白富美，从此走向人生巅峰</t>
+  </si>
+  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -251,10 +270,10 @@
     <t>代码测试语言扫描</t>
   </si>
   <si>
-    <t>Test1234</t>
-  </si>
-  <si>
-    <t>预制体测试语言扫描</t>
+    <t>TipStart</t>
+  </si>
+  <si>
+    <t>点击小明小美亲吻，但是小心老板看见！ 另外注意门和窗户啦！</t>
   </si>
   <si>
     <t>UNLOCK</t>
@@ -266,23 +285,366 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -290,9 +652,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -300,17 +904,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -424,6 +1072,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -449,815 +1105,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -1563,10 +1411,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1058">
+            <xdr:cNvPr hidden="1" name="A1" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1649,10 +1497,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1059">
+            <xdr:cNvPr hidden="1" name="A2" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1735,10 +1583,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1060">
+            <xdr:cNvPr hidden="1" name="A3" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1821,10 +1669,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1061">
+            <xdr:cNvPr hidden="1" name="A4" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1907,10 +1755,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1062">
+            <xdr:cNvPr hidden="1" name="A5" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1993,10 +1841,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1063">
+            <xdr:cNvPr hidden="1" name="A6" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2079,10 +1927,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1064">
+            <xdr:cNvPr hidden="1" name="A7" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2165,10 +2013,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1065">
+            <xdr:cNvPr hidden="1" name="A8" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2251,10 +2099,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1066">
+            <xdr:cNvPr hidden="1" name="A9" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2337,10 +2185,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1067">
+            <xdr:cNvPr hidden="1" name="A10" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2423,10 +2271,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1068">
+            <xdr:cNvPr hidden="1" name="A11" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2509,10 +2357,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1069">
+            <xdr:cNvPr hidden="1" name="A12" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2595,10 +2443,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1070">
+            <xdr:cNvPr hidden="1" name="A13" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2681,10 +2529,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1071">
+            <xdr:cNvPr hidden="1" name="A14" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2767,10 +2615,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1072">
+            <xdr:cNvPr hidden="1" name="A15" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2853,10 +2701,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1073">
+            <xdr:cNvPr hidden="1" name="A16" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2939,10 +2787,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1074">
+            <xdr:cNvPr hidden="1" name="A17" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3025,10 +2873,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1075">
+            <xdr:cNvPr hidden="1" name="A18" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3111,10 +2959,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1076">
+            <xdr:cNvPr hidden="1" name="A19" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3197,10 +3045,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1077">
+            <xdr:cNvPr hidden="1" name="A20" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3283,10 +3131,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1078">
+            <xdr:cNvPr hidden="1" name="A21" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3369,10 +3217,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1079">
+            <xdr:cNvPr hidden="1" name="A22" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3455,10 +3303,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1080">
+            <xdr:cNvPr hidden="1" name="A23" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3541,10 +3389,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1081">
+            <xdr:cNvPr hidden="1" name="A24" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3627,10 +3475,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1082">
+            <xdr:cNvPr hidden="1" name="A25" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3713,10 +3561,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1083">
+            <xdr:cNvPr hidden="1" name="A26" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3799,10 +3647,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1084">
+            <xdr:cNvPr hidden="1" name="A27" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3885,10 +3733,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1085">
+            <xdr:cNvPr hidden="1" name="A28" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3971,10 +3819,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1086">
+            <xdr:cNvPr hidden="1" name="A29" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4057,10 +3905,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1087">
+            <xdr:cNvPr hidden="1" name="A30" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4143,10 +3991,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1088">
+            <xdr:cNvPr hidden="1" name="A31" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4229,10 +4077,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1089">
+            <xdr:cNvPr hidden="1" name="A32" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4315,10 +4163,182 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1090">
+            <xdr:cNvPr hidden="1" name="A33" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4430,7 +4450,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -4465,7 +4485,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4639,23 +4659,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
-    <col min="3" max="3" width="38.6902858189174" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4955,19 +4970,36 @@
         <v>65</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1"/>
+      <c r="B34" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId270" name="A1">
+            <control shapeId="1061" r:id="rId74" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4989,7 +5021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId271" name="A2">
+            <control shapeId="1062" r:id="rId75" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5011,7 +5043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId272" name="A3">
+            <control shapeId="1063" r:id="rId76" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5033,7 +5065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId273" name="A4">
+            <control shapeId="1064" r:id="rId77" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5055,7 +5087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId274" name="A5">
+            <control shapeId="1065" r:id="rId78" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5077,7 +5109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId275" name="A6">
+            <control shapeId="1066" r:id="rId79" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5099,7 +5131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId276" name="A7">
+            <control shapeId="1067" r:id="rId80" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5121,7 +5153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId277" name="A8">
+            <control shapeId="1068" r:id="rId81" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5143,7 +5175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId278" name="A9">
+            <control shapeId="1069" r:id="rId82" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5165,7 +5197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId279" name="A10">
+            <control shapeId="1070" r:id="rId83" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5187,7 +5219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId280" name="A11">
+            <control shapeId="1071" r:id="rId84" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5209,7 +5241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId281" name="A12">
+            <control shapeId="1072" r:id="rId85" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5231,7 +5263,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId282" name="A13">
+            <control shapeId="1073" r:id="rId86" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5253,7 +5285,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId283" name="A14">
+            <control shapeId="1074" r:id="rId87" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5275,7 +5307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId284" name="A15">
+            <control shapeId="1075" r:id="rId88" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5297,7 +5329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId285" name="A16">
+            <control shapeId="1076" r:id="rId89" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5319,7 +5351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId286" name="A17">
+            <control shapeId="1077" r:id="rId90" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5341,7 +5373,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId287" name="A18">
+            <control shapeId="1078" r:id="rId91" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5363,7 +5395,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId288" name="A19">
+            <control shapeId="1079" r:id="rId92" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5385,7 +5417,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId289" name="A20">
+            <control shapeId="1080" r:id="rId93" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5407,7 +5439,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId290" name="A21">
+            <control shapeId="1081" r:id="rId94" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5429,7 +5461,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId291" name="A22">
+            <control shapeId="1082" r:id="rId95" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5451,7 +5483,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId292" name="A23">
+            <control shapeId="1083" r:id="rId96" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5473,7 +5505,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId293" name="A24">
+            <control shapeId="1084" r:id="rId97" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5495,7 +5527,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId294" name="A25">
+            <control shapeId="1085" r:id="rId98" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5517,7 +5549,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId295" name="A26">
+            <control shapeId="1086" r:id="rId99" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5539,7 +5571,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId296" name="A27">
+            <control shapeId="1087" r:id="rId100" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5561,7 +5593,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId297" name="A28">
+            <control shapeId="1088" r:id="rId101" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5583,7 +5615,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId298" name="A29">
+            <control shapeId="1089" r:id="rId102" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5605,7 +5637,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId299" name="A30">
+            <control shapeId="1090" r:id="rId103" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5627,7 +5659,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId300" name="A31">
+            <control shapeId="1091" r:id="rId104" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5649,7 +5681,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId301" name="A32">
+            <control shapeId="1092" r:id="rId105" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5671,7 +5703,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId302" name="A33">
+            <control shapeId="1093" r:id="rId106" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5684,6 +5716,50 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>33</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId107" name="A34">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId108" name="A35">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>35</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/GF_X-master/AAAGameData/Languages/ChineseSimplified.xlsx
+++ b/GF_X-master/AAAGameData/Languages/ChineseSimplified.xlsx
@@ -1395,6 +1395,286 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -1411,10 +1691,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1497,10 +1777,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1062">
+            <xdr:cNvPr hidden="1" name="A2" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1583,10 +1863,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1063">
+            <xdr:cNvPr hidden="1" name="A3" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1669,10 +1949,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1064">
+            <xdr:cNvPr hidden="1" name="A4" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1755,10 +2035,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1065">
+            <xdr:cNvPr hidden="1" name="A5" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1841,10 +2121,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1066">
+            <xdr:cNvPr hidden="1" name="A6" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1927,10 +2207,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1067">
+            <xdr:cNvPr hidden="1" name="A7" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2013,10 +2293,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1068">
+            <xdr:cNvPr hidden="1" name="A8" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2099,10 +2379,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1069">
+            <xdr:cNvPr hidden="1" name="A9" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2185,10 +2465,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1070">
+            <xdr:cNvPr hidden="1" name="A10" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2271,10 +2551,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1071">
+            <xdr:cNvPr hidden="1" name="A11" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2357,10 +2637,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1072">
+            <xdr:cNvPr hidden="1" name="A12" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2443,10 +2723,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1073">
+            <xdr:cNvPr hidden="1" name="A13" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2529,10 +2809,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1074">
+            <xdr:cNvPr hidden="1" name="A14" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2615,10 +2895,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1075">
+            <xdr:cNvPr hidden="1" name="A15" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2701,10 +2981,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1076">
+            <xdr:cNvPr hidden="1" name="A16" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2787,10 +3067,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1077">
+            <xdr:cNvPr hidden="1" name="A17" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2873,10 +3153,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1078">
+            <xdr:cNvPr hidden="1" name="A18" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2959,10 +3239,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1079">
+            <xdr:cNvPr hidden="1" name="A19" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3045,10 +3325,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1080">
+            <xdr:cNvPr hidden="1" name="A20" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3131,10 +3411,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1081">
+            <xdr:cNvPr hidden="1" name="A21" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3217,10 +3497,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1082">
+            <xdr:cNvPr hidden="1" name="A22" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3303,10 +3583,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1083">
+            <xdr:cNvPr hidden="1" name="A23" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3389,10 +3669,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1084">
+            <xdr:cNvPr hidden="1" name="A24" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3475,10 +3755,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1085">
+            <xdr:cNvPr hidden="1" name="A25" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3561,10 +3841,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1086">
+            <xdr:cNvPr hidden="1" name="A26" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3647,10 +3927,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1087">
+            <xdr:cNvPr hidden="1" name="A27" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3733,10 +4013,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1088">
+            <xdr:cNvPr hidden="1" name="A28" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3819,10 +4099,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1089">
+            <xdr:cNvPr hidden="1" name="A29" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3905,10 +4185,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1090">
+            <xdr:cNvPr hidden="1" name="A30" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3991,10 +4271,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1091">
+            <xdr:cNvPr hidden="1" name="A31" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4077,10 +4357,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1092">
+            <xdr:cNvPr hidden="1" name="A32" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4163,10 +4443,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1093">
+            <xdr:cNvPr hidden="1" name="A33" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4249,10 +4529,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1094">
+            <xdr:cNvPr hidden="1" name="A34" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4335,10 +4615,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1095">
+            <xdr:cNvPr hidden="1" name="A35" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4999,7 +5279,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId74" name="A1">
+            <control shapeId="1060" r:id="rId142" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5021,7 +5301,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId75" name="A2">
+            <control shapeId="1061" r:id="rId143" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5043,7 +5323,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId76" name="A3">
+            <control shapeId="1062" r:id="rId144" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5065,7 +5345,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId77" name="A4">
+            <control shapeId="1063" r:id="rId145" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5087,7 +5367,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId78" name="A5">
+            <control shapeId="1064" r:id="rId146" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5109,7 +5389,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId79" name="A6">
+            <control shapeId="1065" r:id="rId147" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5131,7 +5411,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId80" name="A7">
+            <control shapeId="1066" r:id="rId148" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5153,7 +5433,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId81" name="A8">
+            <control shapeId="1067" r:id="rId149" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5175,7 +5455,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId82" name="A9">
+            <control shapeId="1068" r:id="rId150" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5197,7 +5477,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId83" name="A10">
+            <control shapeId="1069" r:id="rId151" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5219,7 +5499,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId84" name="A11">
+            <control shapeId="1070" r:id="rId152" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5241,7 +5521,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId85" name="A12">
+            <control shapeId="1071" r:id="rId153" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5263,7 +5543,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId86" name="A13">
+            <control shapeId="1072" r:id="rId154" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5285,7 +5565,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId87" name="A14">
+            <control shapeId="1073" r:id="rId155" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5307,7 +5587,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId88" name="A15">
+            <control shapeId="1074" r:id="rId156" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5329,7 +5609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId89" name="A16">
+            <control shapeId="1075" r:id="rId157" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5351,7 +5631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId90" name="A17">
+            <control shapeId="1076" r:id="rId158" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5373,7 +5653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId91" name="A18">
+            <control shapeId="1077" r:id="rId159" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5395,7 +5675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId92" name="A19">
+            <control shapeId="1078" r:id="rId160" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5417,7 +5697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId93" name="A20">
+            <control shapeId="1079" r:id="rId161" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5439,7 +5719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId94" name="A21">
+            <control shapeId="1080" r:id="rId162" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5461,7 +5741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId95" name="A22">
+            <control shapeId="1081" r:id="rId163" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5483,7 +5763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId96" name="A23">
+            <control shapeId="1082" r:id="rId164" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5505,7 +5785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId97" name="A24">
+            <control shapeId="1083" r:id="rId165" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5527,7 +5807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId98" name="A25">
+            <control shapeId="1084" r:id="rId166" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5549,7 +5829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId99" name="A26">
+            <control shapeId="1085" r:id="rId167" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5571,7 +5851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId100" name="A27">
+            <control shapeId="1086" r:id="rId168" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5593,7 +5873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId101" name="A28">
+            <control shapeId="1087" r:id="rId169" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5615,7 +5895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId102" name="A29">
+            <control shapeId="1088" r:id="rId170" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5637,7 +5917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId103" name="A30">
+            <control shapeId="1089" r:id="rId171" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5659,7 +5939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId104" name="A31">
+            <control shapeId="1090" r:id="rId172" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5681,7 +5961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId105" name="A32">
+            <control shapeId="1091" r:id="rId173" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5703,7 +5983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId106" name="A33">
+            <control shapeId="1092" r:id="rId174" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5725,7 +6005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId107" name="A34">
+            <control shapeId="1093" r:id="rId175" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5747,7 +6027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId108" name="A35">
+            <control shapeId="1094" r:id="rId176" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
